--- a/public/tool/app/http-qualification-query-helper/template.xlsx
+++ b/public/tool/app/http-qualification-query-helper/template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,7 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -57,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -433,14 +435,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>员工号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>示例姓名</t>
         </is>
       </c>
     </row>
